--- a/excel/import_data.xlsx
+++ b/excel/import_data.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7683DBC-6D44-46DE-B11B-67431C88665B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Data Siswa" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Data Siswa" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>Nama Siswa</t>
   </si>
@@ -59,18 +55,39 @@
     <t/>
   </si>
   <si>
+    <t>Afdhal</t>
+  </si>
+  <si>
+    <t>1231313</t>
+  </si>
+  <si>
+    <t>Laki-Laki</t>
+  </si>
+  <si>
     <t>Islam</t>
   </si>
   <si>
+    <t>Pekanbaru</t>
+  </si>
+  <si>
     <t>09-09-2010</t>
   </si>
   <si>
+    <t>Kaka</t>
+  </si>
+  <si>
     <t>081234567890</t>
   </si>
   <si>
     <t>Jln Kelayapan</t>
   </si>
   <si>
+    <t>10-07-2023</t>
+  </si>
+  <si>
+    <t>2023/2024</t>
+  </si>
+  <si>
     <t>Aktif</t>
   </si>
   <si>
@@ -96,48 +113,30 @@
   </si>
   <si>
     <t>Aktif / Alumni / Berhenti</t>
-  </si>
-  <si>
-    <t>Febriana Valentine</t>
-  </si>
-  <si>
-    <t>Perempuan</t>
-  </si>
-  <si>
-    <t>Serang</t>
-  </si>
-  <si>
-    <t>Siti</t>
-  </si>
-  <si>
-    <t>2025/2026</t>
-  </si>
-  <si>
-    <t>20-06-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1F4E79"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF333333"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -151,8 +150,8 @@
     </font>
     <font>
       <i/>
+      <color rgb="FF595959"/>
       <sz val="10"/>
-      <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -212,6 +211,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -220,9 +222,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,9 +561,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
@@ -582,7 +581,7 @@
     <col min="16" max="17" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="25" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,126 +634,126 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="3">
-        <v>33333333</v>
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3">
         <v>1</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O4" s="4" t="s">
+      <c r="P3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O5" s="4" t="s">
+      <c r="P4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O6" s="4" t="s">
+      <c r="P5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O7" s="4" t="s">
+      <c r="P6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O8" s="4" t="s">
+      <c r="P7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O9" s="4" t="s">
+      <c r="P8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="15:17" x14ac:dyDescent="0.25">
+      <c r="O9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="6" t="s">
+      <c r="P9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -763,6 +762,6 @@
     <mergeCell ref="O2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>